--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_648_Russia_Baltic_Sea.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_648_Russia_Baltic_Sea.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R0047cce1cdbb46c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R7bef445e3af246ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rd3def8486d8448f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R1c7c7094c7fe49fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R2fe9ee328ab5407e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R2047f650868e477f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rd2c91feb40e54dcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R7d5e8c138d8f4d51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R05e8c76404174b2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R84e77d473c1b4b26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R4514ed1c6a034816"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R8f2b2354912345a3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ648CommercialTable" displayName="EEZ648CommercialTable" ref="A1:O9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O9"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ648CommercialTable" displayName="EEZ648CommercialTable" ref="A1:E9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E9"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ648FunctionalTable" displayName="EEZ648FunctionalTable" ref="A1:O14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O14"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ648FunctionalTable" displayName="EEZ648FunctionalTable" ref="A1:E14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E14"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ648ValidationTable" displayName="EEZ648ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ648ValidationTable" displayName="EEZ648ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -3843,7 +3797,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raac123de0fe244a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R564268e6daaa44af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3853,20 +3807,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -3874,498 +3818,174 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>4911.4926597525</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.0894521275482605</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1228.7177370733634</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>4911.4926597525</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1229.0887898622332</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$48,A2,'Species'!$U$2:$U$48))</x:f>
-        <x:v>6036660.569592441</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.0894521275482605</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1228.7177370733634</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>6034838.146543527</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>1822.4230489144102</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0003019837491347</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0003019837491347152</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1661.9124213848002</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.4887714069835014</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>308.15655262728194</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1661.9124213848002</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>344.8942447256753</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$48,A3,'Species'!$U$2:$U$48))</x:f>
-        <x:v>573184.0293737289</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.4887714069835014</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>308.15655262728194</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>512129.2025423987</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>61054.826831330196</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1192176242405851</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.11921762424058512</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>99371.3445396337</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.2015982610913802</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>159.07365544520604</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>99371.3445396337</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>173.6893624736093</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$48,A4,'Species'!$U$2:$U$48))</x:f>
-        <x:v>17259745.481234353</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.2015982610913802</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>159.07365544520604</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>15807363.022424549</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1452382.4588098042</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0918801230002395</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.09188012300023944</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>0.0000337339</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.06</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>114.81536214968828</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>0.0000337339</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>114.81536214968828</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$48,A5,'Species'!$U$2:$U$48))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>0.0038731699452213696</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.06</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>114.81536214968828</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>0.0038731699452213696</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>3537.7020071371</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.8747385626389077</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>74.94429225355478</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>3537.7020071371</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>97.64138756610913</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$48,A6,'Species'!$U$2:$U$48))</x:f>
-        <x:v>345426.1327722757</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.8747385626389077</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>74.94429225355478</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>265130.57312887016</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>80295.55964340555</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.3028528875256375</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.3028528875256376</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1239.4446050946</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.8686243406159937</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>738.9658022021389</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1239.4446050946</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1037.5391491900207</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$48,A7,'Species'!$U$2:$U$48))</x:f>
-        <x:v>1285972.3010380126</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.8686243406159937</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>738.9658022021389</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>915907.1768888443</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>370065.12414916826</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.404042170961261</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.4040421709612609</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>572.3645247595001</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.5387399475684616</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>345.73229380576845</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>572.3645247595001</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>485.0285715622575</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$48,A8,'Species'!$U$2:$U$48))</x:f>
-        <x:v>277613.1478570107</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.5387399475684616</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>345.73229380576845</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>197884.90003815052</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>79728.2478188602</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.4029021304985336</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.4029021304985336</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>0.0084875681</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.69</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>489.77881936844614</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>0.0084875681</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>489.7788193684461</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$48,A9,'Species'!$U$2:$U$48))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>4.157031083327285</x:v>
       </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.69</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>489.77881936844614</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>4.157031083327285</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G9">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O9">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R348c58b3cec349c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fc1926c06b24e41"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4375,20 +3995,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4396,768 +4006,269 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>4933.308364257799</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.092179355154213</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1236.457961050758</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>4933.308364257799</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1240.7811984376035</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$48,A2,'Species'!$U$2:$U$48))</x:f>
-        <x:v>6121156.264466045</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.092179355154213</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1236.457961050758</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>6099828.401304849</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>21327.863161196</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0034964693689798</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.003496469368979894</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>91.30097772819998</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.8931488299483483</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>781.8957093525395</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>91.30097772819998</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>871.1074148995269</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$48,A3,'Species'!$U$2:$U$48))</x:f>
-        <x:v>79532.95868661157</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.8931488299483483</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>781.8957093525395</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>71387.84274537134</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>8145.115941240234</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1140966812835698</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.1140966812835698</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>5.9005369894</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.341152076182254</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2193.5729206913315</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>5.9005369894</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2254.7327976036954</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$48,A4,'Species'!$U$2:$U$48))</x:f>
-        <x:v>13304.134273473948</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.341152076182254</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2193.5729206913315</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>12943.258157485394</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>360.8761159885544</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0278813967547924</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.027881396754792467</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>769.7905214883</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.9879435780387262</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>972.6208562004807</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>769.7905214883</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1030.0762927155752</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$48,A5,'Species'!$U$2:$U$48))</x:f>
-        <x:v>792942.9665422573</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.9879435780387262</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>972.6208562004807</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>748714.3161049649</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>44228.65043729241</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.059072799178441</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.05907279917844103</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>294.31991077370003</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.960476508976869</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>91.3012049063052</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>294.31991077370003</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>91.72638788407264</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$48,A6,'Species'!$U$2:$U$48))</x:f>
-        <x:v>26996.902297634057</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.960476508976869</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>91.3012049063052</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>26871.76248155505</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>125.13981607900496</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0046569262498097</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0046569262498096925</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>3203.9945070263</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.9117325074741878</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>81.60795732898129</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>3203.9945070263</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>204.94359257952158</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$48,A7,'Species'!$U$2:$U$48))</x:f>
-        <x:v>656638.1448750232</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.9117325074741878</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>81.60795732898129</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>261471.44701169274</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>395166.6978633304</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>2.511318740075122</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>1.5113187400751218</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>52069.708114663204</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.3812890863180507</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>240.5963786904339</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>52069.708114663204</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>241.44344901488134</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$48,A8,'Species'!$U$2:$U$48))</x:f>
-        <x:v>12571889.916402439</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.3812890863180507</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>240.5963786904339</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>12527783.211855868</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>44106.70454657078</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0035207110308892</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.003520711030889303</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>0.0000337339</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.06</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>114.81536214968828</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>0.0000337339</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>114.81536214968828</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$48,A9,'Species'!$U$2:$U$48))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>0.0038731699452213696</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.06</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>114.81536214968828</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>0.0038731699452213696</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>13.5092344123</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.3100000000000005</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>204.17379446695315</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>13.5092344123</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$48,A10,'Species'!$U$2:$U$48))</x:f>
-        <x:v>2758.2316503028283</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.3100000000000005</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>204.17379446695315</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2758.231650302831</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>-2.7284841053187847e-12</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>0.999999999999999</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>-9.892149939687697e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>106.96503352469999</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.290334085287383</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>195.13451138984038</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>106.96503352469999</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>197.96519364876056</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$48,A11,'Species'!$U$2:$U$48))</x:f>
-        <x:v>21175.3535753634</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.290334085287383</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>195.13451138984038</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>20872.56955264023</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>302.78402272316816</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0145063127929483</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.014506312792948301</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>47952.0491334899</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.0100000000000002</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>102.32929922807547</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>47952.0491334899</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>102.32929922807537</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$48,A12,'Species'!$U$2:$U$48))</x:f>
-        <x:v>4906899.58438026</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.0100000000000002</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>102.32929922807547</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>4906899.584380264</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>-4.6566128730773926e-9</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>0.999999999999999</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>-9.489929013221324e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>197.4110265811</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.1100000000000003</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>128.82495516931348</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>197.4110265811</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$48,A13,'Species'!$U$2:$U$48))</x:f>
-        <x:v>25431.466649238337</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.1100000000000003</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>128.82495516931348</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>25431.466649238362</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>-2.546585164964199e-11</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>0.999999999999999</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>-1.001352065174922e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>1656.0118843954</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.485734288883656</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>306.00906286744157</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>1656.0118843954</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>338.08929777376795</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$48,A14,'Species'!$U$2:$U$48))</x:f>
-        <x:v>559879.895100255</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.485734288883656</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>306.00906286744157</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>506754.6448411824</x:v>
       </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>53125.250259072636</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.1048342640761037</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.10483426407610366</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G14">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O14">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04bcd6b16d024f7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94a2bca2e08942a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5332,7 +4443,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -5431,7 +4542,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>25778605.822772074</x:v>
+        <x:v>23733257.182470594</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5445,7 +4556,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>25778605.82277207</x:v>
+        <x:v>25211716.740608588</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5459,7 +4570,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-3.725290298461914e-9</x:v>
+        <x:v>-2045348.6403014846</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5473,7 +4584,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-7.450580596923828e-9</x:v>
+        <x:v>-566889.0821634904</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5484,9 +4595,9 @@
         <x:v>EEZ_648</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -5498,47 +4609,19 @@
         <x:v>EEZ_648</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_648</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_648</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8deeb569c57455b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbaafda9d2a6c4354"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5585,7 +4668,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
